--- a/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_23-10-2026.xlsx
+++ b/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_23-10-2026.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.roofingoutlet.co.uk/products/powerlon-ultraperm-standard-breather-membrane-roof-felt-1m-x-50m</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -862,28 +862,28 @@
   (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff7a5103f45]
-	(No symbol) [0x7ff7a5004f90]
-	(No symbol) [0x7ff7a54097ad]
-	(No symbol) [0x7ff7a5693188]
-	(No symbol) [0x7ff7a4e765d6]
-	(No symbol) [0x7ff7a4e771b2]
-	(No symbol) [0x7ff7a4e83dc0]
-	(No symbol) [0x7ff7a4eb34f4]
-	(No symbol) [0x7ff7a4ea9a8a]
-	(No symbol) [0x7ff7a4eb25d1]
-	(No symbol) [0x7ff7a4e97cb9]
-	(No symbol) [0x7ff7a4e98ff3]
-	(No symbol) [0x7ff7a55be1a1]
-	(No symbol) [0x7ff7a55e181b]
-	(No symbol) [0x7ff7a55d7ece]
-	(No symbol) [0x7ff7a522b10e]
-	(No symbol) [0x7ff7a5013db5]
-	(No symbol) [0x7ff7a500e694]
-	(No symbol) [0x7ff7a500e824]
-	(No symbol) [0x7ff7a4ff6bdc]
-	(No symbol) [0x7ffb2f60dda7]
-	(No symbol) [0x7ffb3069ee4c]
+	(No symbol) [0x7ff76d353f45]
+	(No symbol) [0x7ff76d254f90]
+	(No symbol) [0x7ff76d6597ad]
+	(No symbol) [0x7ff76d8e3188]
+	(No symbol) [0x7ff76d0c65d6]
+	(No symbol) [0x7ff76d0c71b2]
+	(No symbol) [0x7ff76d0d3dc0]
+	(No symbol) [0x7ff76d1034f4]
+	(No symbol) [0x7ff76d0f9a8a]
+	(No symbol) [0x7ff76d1025d1]
+	(No symbol) [0x7ff76d0e7cb9]
+	(No symbol) [0x7ff76d0e8ff3]
+	(No symbol) [0x7ff76d80e1a1]
+	(No symbol) [0x7ff76d83181b]
+	(No symbol) [0x7ff76d827ece]
+	(No symbol) [0x7ff76d47b10e]
+	(No symbol) [0x7ff76d263db5]
+	(No symbol) [0x7ff76d25e694]
+	(No symbol) [0x7ff76d25e824]
+	(No symbol) [0x7ff76d246bdc]
+	(No symbol) [0x7ffa3257dda7]
+	(No symbol) [0x7ffa33b7ee4c]
 </t>
         </is>
       </c>
@@ -1813,28 +1813,28 @@
   (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff7a5103f45]
-	(No symbol) [0x7ff7a5004f90]
-	(No symbol) [0x7ff7a54097ad]
-	(No symbol) [0x7ff7a5693188]
-	(No symbol) [0x7ff7a4e765d6]
-	(No symbol) [0x7ff7a4e771b2]
-	(No symbol) [0x7ff7a4e83dc0]
-	(No symbol) [0x7ff7a4eb34f4]
-	(No symbol) [0x7ff7a4ea9a8a]
-	(No symbol) [0x7ff7a4eb25d1]
-	(No symbol) [0x7ff7a4e97cb9]
-	(No symbol) [0x7ff7a4e98ff3]
-	(No symbol) [0x7ff7a55be1a1]
-	(No symbol) [0x7ff7a55e181b]
-	(No symbol) [0x7ff7a55d7ece]
-	(No symbol) [0x7ff7a522b10e]
-	(No symbol) [0x7ff7a5013db5]
-	(No symbol) [0x7ff7a500e694]
-	(No symbol) [0x7ff7a500e824]
-	(No symbol) [0x7ff7a4ff6bdc]
-	(No symbol) [0x7ffb2f60dda7]
-	(No symbol) [0x7ffb3069ee4c]
+	(No symbol) [0x7ff76d353f45]
+	(No symbol) [0x7ff76d254f90]
+	(No symbol) [0x7ff76d6597ad]
+	(No symbol) [0x7ff76d8e3188]
+	(No symbol) [0x7ff76d0c65d6]
+	(No symbol) [0x7ff76d0c71b2]
+	(No symbol) [0x7ff76d0d3dc0]
+	(No symbol) [0x7ff76d1034f4]
+	(No symbol) [0x7ff76d0f9a8a]
+	(No symbol) [0x7ff76d1025d1]
+	(No symbol) [0x7ff76d0e7cb9]
+	(No symbol) [0x7ff76d0e8ff3]
+	(No symbol) [0x7ff76d80e1a1]
+	(No symbol) [0x7ff76d83181b]
+	(No symbol) [0x7ff76d827ece]
+	(No symbol) [0x7ff76d47b10e]
+	(No symbol) [0x7ff76d263db5]
+	(No symbol) [0x7ff76d25e694]
+	(No symbol) [0x7ff76d25e824]
+	(No symbol) [0x7ff76d246bdc]
+	(No symbol) [0x7ffa3257dda7]
+	(No symbol) [0x7ffa33b7ee4c]
 </t>
         </is>
       </c>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>£13.87</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
